--- a/data/trans_orig/ProblemasDormirP33b-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario en 2023</t>
+          <t>Población con problemas para dormir a diario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111455</t>
+          <t>112415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147905</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256876</t>
+          <t>254545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>297566</t>
+          <t>296515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>376816</t>
+          <t>376094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>435007</t>
+          <t>431184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>367033</t>
+          <t>365386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403483</t>
+          <t>402523</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>457942</t>
+          <t>458993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>498632</t>
+          <t>500963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>835439</t>
+          <t>839262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>893630</t>
+          <t>894352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150943</t>
+          <t>147067</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>248880</t>
+          <t>252693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>235713</t>
+          <t>243834</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>369981</t>
+          <t>368334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>414760</t>
+          <t>436494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>604264</t>
+          <t>607526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2041447</t>
+          <t>2037634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2139384</t>
+          <t>2143260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1867842</t>
+          <t>1869489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2002110</t>
+          <t>1993989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3923886</t>
+          <t>3920624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4113390</t>
+          <t>4091656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59035</t>
+          <t>59563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96405</t>
+          <t>95976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85088</t>
+          <t>84933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115827</t>
+          <t>117801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150958</t>
+          <t>149770</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202362</t>
+          <t>199236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>550218</t>
+          <t>550647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>587588</t>
+          <t>587060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>544636</t>
+          <t>542662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575375</t>
+          <t>575530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1104724</t>
+          <t>1107850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1156128</t>
+          <t>1157316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>325997</t>
+          <t>327611</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>465529</t>
+          <t>468230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>552520</t>
+          <t>563469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>761376</t>
+          <t>756062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>971342</t>
+          <t>960797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1203844</t>
+          <t>1203699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2986360</t>
+          <t>2983659</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3125892</t>
+          <t>3124278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2892418</t>
+          <t>2897732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3101274</t>
+          <t>3090325</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5901839</t>
+          <t>5901984</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6134341</t>
+          <t>6144886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProblemasDormirP33b-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>128248</t>
+          <t>138058</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112415</t>
+          <t>119461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149552</t>
+          <t>157628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,67 +760,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>275570</t>
+          <t>301294</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>254545</t>
+          <t>280549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>296515</t>
+          <t>322449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>34,13%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>39,23%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>439352</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>409285</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>471806</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>31,37%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>29,22%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>33,69%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>39,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>403818</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>376094</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>431184</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>386690</t>
+          <t>440471</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>365386</t>
+          <t>420901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402523</t>
+          <t>459068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,67 +873,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>479938</t>
+          <t>520744</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>458993</t>
+          <t>499589</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>500963</t>
+          <t>541489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>65,87%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>961215</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>928761</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>991282</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>68,63%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>66,31%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>866628</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>839262</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>894352</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>68,21%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>66,06%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,78%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>212174</t>
+          <t>234656</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147067</t>
+          <t>206828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>252693</t>
+          <t>266289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>319978</t>
+          <t>361716</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>243834</t>
+          <t>332177</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>368334</t>
+          <t>394831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>532152</t>
+          <t>596373</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>436494</t>
+          <t>554051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>607526</t>
+          <t>641593</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2078153</t>
+          <t>1995910</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2037634</t>
+          <t>1964277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2143260</t>
+          <t>2023738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1917845</t>
+          <t>1809676</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1869489</t>
+          <t>1776561</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1993989</t>
+          <t>1839215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3995998</t>
+          <t>3805586</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3920624</t>
+          <t>3760366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4091656</t>
+          <t>3847908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75132</t>
+          <t>84295</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59563</t>
+          <t>64940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95976</t>
+          <t>104890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>99804</t>
+          <t>112670</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84933</t>
+          <t>95254</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117801</t>
+          <t>129746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>174936</t>
+          <t>196965</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149770</t>
+          <t>173043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199236</t>
+          <t>223293</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>571491</t>
+          <t>627292</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>550647</t>
+          <t>606697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>587060</t>
+          <t>646647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>560659</t>
+          <t>622207</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542662</t>
+          <t>605131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575530</t>
+          <t>639623</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1132150</t>
+          <t>1249499</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1107850</t>
+          <t>1223171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1157316</t>
+          <t>1273421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>415554</t>
+          <t>457009</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>327611</t>
+          <t>416449</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>468230</t>
+          <t>501093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>695352</t>
+          <t>775680</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>563469</t>
+          <t>728042</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>756062</t>
+          <t>814736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1110906</t>
+          <t>1232689</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>960797</t>
+          <t>1176169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1203699</t>
+          <t>1296996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3036335</t>
+          <t>3063674</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2983659</t>
+          <t>3019590</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3124278</t>
+          <t>3104234</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2958442</t>
+          <t>2952627</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2897732</t>
+          <t>2913571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3090325</t>
+          <t>3000265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5994777</t>
+          <t>6016301</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5901984</t>
+          <t>5951994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6144886</t>
+          <t>6072821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
